--- a/Pricing Logic/modules/uploads/module_4_701.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_701.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="10">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,61 +37,13 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>سفن اب ستار كانز - 320 مل</t>
-  </si>
-  <si>
-    <t>سفن اب تربو - 390 مل</t>
-  </si>
-  <si>
-    <t>مناديل فاميليا تواليت 2 طبقة - 2 رول</t>
-  </si>
-  <si>
-    <t>تونة دولفين مفتتة حار 170 جم + 30 جم - 200 جم</t>
-  </si>
-  <si>
-    <t>كلوريل كلور 2*1 برائحة اللافندر - 1 كجم</t>
-  </si>
-  <si>
-    <t>مناديل بابيا تواليت 10 رول + 2 رول هدية - 12 رول</t>
-  </si>
-  <si>
-    <t>مكرونة بساطة فرن - 350 جم</t>
-  </si>
-  <si>
-    <t>سائل اطباق وفير بلس ليمون اصفر - 725 جم</t>
-  </si>
-  <si>
-    <t>هارفست فول مقشور بالفلفل الحار خصم %15 - 400 جم</t>
-  </si>
-  <si>
-    <t>هارفست فول بالخلطة اللبنانية خصم %15 - 400 جم</t>
-  </si>
-  <si>
-    <t>كوكا كولا كانز ستار - 320 مل</t>
-  </si>
-  <si>
-    <t>كلوريل بقوة الاكسجين ازرق - 1 كجم</t>
-  </si>
-  <si>
-    <t>مناديل فاميليا تواليت مضغوط - 2 رول</t>
-  </si>
-  <si>
-    <t>فاين مناديل تواليت كمفورت 2 رول 2 رول</t>
-  </si>
-  <si>
-    <t>فاين سمارت مناديل تواليت مضغوط 5+1 رول * 2 طبقة 6 رول</t>
-  </si>
-  <si>
-    <t>فاين سوبر مناديل مطبخ 2 رول * 2 طبقة 2 رول</t>
-  </si>
-  <si>
-    <t>ديفا منظف ايدى الترا كلين - 500 مل</t>
+    <t>حفاضات بى بم ميجا مقاس 5 - 76 حفاضة</t>
+  </si>
+  <si>
+    <t>فلامنكو ذرة بطعم السوداني  - 10 جنية</t>
   </si>
   <si>
     <t>YES</t>
-  </si>
-  <si>
-    <t>NO</t>
   </si>
 </sst>
 </file>
@@ -449,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -477,376 +429,53 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>140</v>
+        <v>10530</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="D2">
-        <v>331.75</v>
+        <v>777</v>
       </c>
       <c r="E2" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>1006</v>
+        <v>10530</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D3">
-        <v>130</v>
+        <v>388.5</v>
       </c>
       <c r="E3" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>1703</v>
+        <v>13280</v>
       </c>
       <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>92</v>
+      </c>
+      <c r="E4" t="s">
         <v>9</v>
-      </c>
-      <c r="C4">
-        <v>2</v>
-      </c>
-      <c r="D4">
-        <v>182</v>
-      </c>
-      <c r="E4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>2859</v>
-      </c>
-      <c r="B5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5">
-        <v>15</v>
-      </c>
-      <c r="D5">
-        <v>426</v>
-      </c>
-      <c r="E5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>2859</v>
-      </c>
-      <c r="B6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6">
-        <v>1704</v>
-      </c>
-      <c r="E6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>2859</v>
-      </c>
-      <c r="B7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7">
-        <v>11</v>
-      </c>
-      <c r="D7">
-        <v>35.5</v>
-      </c>
-      <c r="E7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>2859</v>
-      </c>
-      <c r="B8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8">
-        <v>16</v>
-      </c>
-      <c r="D8">
-        <v>852</v>
-      </c>
-      <c r="E8" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>3230</v>
-      </c>
-      <c r="B9" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9">
-        <v>1</v>
-      </c>
-      <c r="D9">
-        <v>160.25</v>
-      </c>
-      <c r="E9" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>4033</v>
-      </c>
-      <c r="B10" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10">
-        <v>29</v>
-      </c>
-      <c r="D10">
-        <v>293.25</v>
-      </c>
-      <c r="E10" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>7705</v>
-      </c>
-      <c r="B11" t="s">
-        <v>13</v>
-      </c>
-      <c r="C11">
-        <v>2</v>
-      </c>
-      <c r="D11">
-        <v>171.5</v>
-      </c>
-      <c r="E11" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>8600</v>
-      </c>
-      <c r="B12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C12">
-        <v>1</v>
-      </c>
-      <c r="D12">
-        <v>200</v>
-      </c>
-      <c r="E12" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>10449</v>
-      </c>
-      <c r="B13" t="s">
-        <v>15</v>
-      </c>
-      <c r="C13">
-        <v>10</v>
-      </c>
-      <c r="D13">
-        <v>16.75</v>
-      </c>
-      <c r="E13" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>10449</v>
-      </c>
-      <c r="B14" t="s">
-        <v>15</v>
-      </c>
-      <c r="C14">
-        <v>1</v>
-      </c>
-      <c r="D14">
-        <v>201</v>
-      </c>
-      <c r="E14" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>10454</v>
-      </c>
-      <c r="B15" t="s">
-        <v>16</v>
-      </c>
-      <c r="C15">
-        <v>10</v>
-      </c>
-      <c r="D15">
-        <v>17.25</v>
-      </c>
-      <c r="E15" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>10454</v>
-      </c>
-      <c r="B16" t="s">
-        <v>16</v>
-      </c>
-      <c r="C16">
-        <v>1</v>
-      </c>
-      <c r="D16">
-        <v>207</v>
-      </c>
-      <c r="E16" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17">
-        <v>11396</v>
-      </c>
-      <c r="B17" t="s">
-        <v>17</v>
-      </c>
-      <c r="C17">
-        <v>2</v>
-      </c>
-      <c r="D17">
-        <v>340</v>
-      </c>
-      <c r="E17" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18">
-        <v>12613</v>
-      </c>
-      <c r="B18" t="s">
-        <v>18</v>
-      </c>
-      <c r="C18">
-        <v>1</v>
-      </c>
-      <c r="D18">
-        <v>305</v>
-      </c>
-      <c r="E18" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19">
-        <v>13247</v>
-      </c>
-      <c r="B19" t="s">
-        <v>19</v>
-      </c>
-      <c r="C19">
-        <v>29</v>
-      </c>
-      <c r="D19">
-        <v>321.5</v>
-      </c>
-      <c r="E19" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20">
-        <v>13268</v>
-      </c>
-      <c r="B20" t="s">
-        <v>20</v>
-      </c>
-      <c r="C20">
-        <v>29</v>
-      </c>
-      <c r="D20">
-        <v>181.75</v>
-      </c>
-      <c r="E20" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21">
-        <v>13272</v>
-      </c>
-      <c r="B21" t="s">
-        <v>21</v>
-      </c>
-      <c r="C21">
-        <v>29</v>
-      </c>
-      <c r="D21">
-        <v>292.75</v>
-      </c>
-      <c r="E21" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22">
-        <v>13273</v>
-      </c>
-      <c r="B22" t="s">
-        <v>22</v>
-      </c>
-      <c r="C22">
-        <v>29</v>
-      </c>
-      <c r="D22">
-        <v>239.5</v>
-      </c>
-      <c r="E22" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23">
-        <v>23330</v>
-      </c>
-      <c r="B23" t="s">
-        <v>23</v>
-      </c>
-      <c r="C23">
-        <v>1</v>
-      </c>
-      <c r="D23">
-        <v>411</v>
-      </c>
-      <c r="E23" t="s">
-        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/uploads/module_4_701.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_701.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="12">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,10 +37,16 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>حفاضات بى بم ميجا مقاس 5 - 76 حفاضة</t>
-  </si>
-  <si>
-    <t>فلامنكو ذرة بطعم السوداني  - 10 جنية</t>
+    <t>سبرايت جيب - 240 مل</t>
+  </si>
+  <si>
+    <t>طوفى توفيكس بالفواكه - 1445 جم</t>
+  </si>
+  <si>
+    <t>مكرونة بساطة فرن - 350 جم</t>
+  </si>
+  <si>
+    <t>فريدا  هوم  فل - 480 مل</t>
   </si>
   <si>
     <t>YES</t>
@@ -401,7 +407,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -429,41 +435,41 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>10530</v>
+        <v>616</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
       </c>
       <c r="C2">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="D2">
-        <v>777</v>
+        <v>290</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>10530</v>
+        <v>1080</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3">
-        <v>80</v>
+        <v>3</v>
       </c>
       <c r="D3">
-        <v>388.5</v>
+        <v>213.25</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>13280</v>
+        <v>1080</v>
       </c>
       <c r="B4" t="s">
         <v>8</v>
@@ -472,10 +478,61 @@
         <v>1</v>
       </c>
       <c r="D4">
-        <v>92</v>
+        <v>1279.5</v>
       </c>
       <c r="E4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>7705</v>
+      </c>
+      <c r="B5" t="s">
         <v>9</v>
+      </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
+      <c r="D5">
+        <v>169.75</v>
+      </c>
+      <c r="E5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>21955</v>
+      </c>
+      <c r="B6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6">
+        <v>10</v>
+      </c>
+      <c r="D6">
+        <v>70</v>
+      </c>
+      <c r="E6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>21955</v>
+      </c>
+      <c r="B7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>840</v>
+      </c>
+      <c r="E7" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/uploads/module_4_701.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_701.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="10">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,16 +37,10 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>سبرايت جيب - 240 مل</t>
-  </si>
-  <si>
-    <t>طوفى توفيكس بالفواكه - 1445 جم</t>
-  </si>
-  <si>
-    <t>مكرونة بساطة فرن - 350 جم</t>
-  </si>
-  <si>
-    <t>فريدا  هوم  فل - 480 مل</t>
+    <t>حفاضات جود كير مقاس 5 - 100 حفاضة</t>
+  </si>
+  <si>
+    <t>فلامنكو ذرة بطعم السوداني  - 10 جنية</t>
   </si>
   <si>
     <t>YES</t>
@@ -407,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -435,41 +429,41 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>616</v>
+        <v>6097</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="D2">
-        <v>290</v>
+        <v>865</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>1080</v>
+        <v>6097</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C3">
-        <v>3</v>
+        <v>80</v>
       </c>
       <c r="D3">
-        <v>213.25</v>
+        <v>432.5</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>1080</v>
+        <v>13280</v>
       </c>
       <c r="B4" t="s">
         <v>8</v>
@@ -478,61 +472,10 @@
         <v>1</v>
       </c>
       <c r="D4">
-        <v>1279.5</v>
+        <v>93.75</v>
       </c>
       <c r="E4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>7705</v>
-      </c>
-      <c r="B5" t="s">
         <v>9</v>
-      </c>
-      <c r="C5">
-        <v>2</v>
-      </c>
-      <c r="D5">
-        <v>169.75</v>
-      </c>
-      <c r="E5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>21955</v>
-      </c>
-      <c r="B6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6">
-        <v>10</v>
-      </c>
-      <c r="D6">
-        <v>70</v>
-      </c>
-      <c r="E6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>21955</v>
-      </c>
-      <c r="B7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7">
-        <v>1</v>
-      </c>
-      <c r="D7">
-        <v>840</v>
-      </c>
-      <c r="E7" t="s">
-        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/uploads/module_4_701.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_701.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="12">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,10 +37,16 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>حفاضات جود كير مقاس 5 - 100 حفاضة</t>
-  </si>
-  <si>
-    <t>فلامنكو ذرة بطعم السوداني  - 10 جنية</t>
+    <t>لوبيا الضحى بلدى - 500 جم</t>
+  </si>
+  <si>
+    <t>ميزة أرز رفيع- 1 كجم</t>
+  </si>
+  <si>
+    <t>ماكسي كـولا - 2 لتر</t>
+  </si>
+  <si>
+    <t>بيبسى كانز ستار زيادة %10- 355 مل</t>
   </si>
   <si>
     <t>YES</t>
@@ -401,7 +407,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -429,53 +435,87 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>6097</v>
+        <v>1063</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
       </c>
       <c r="C2">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="D2">
-        <v>865</v>
+        <v>1835</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>6097</v>
+        <v>1063</v>
       </c>
       <c r="B3" t="s">
         <v>7</v>
       </c>
       <c r="C3">
-        <v>80</v>
+        <v>7</v>
       </c>
       <c r="D3">
-        <v>432.5</v>
+        <v>91.75</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>13280</v>
+        <v>11555</v>
       </c>
       <c r="B4" t="s">
         <v>8</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4">
-        <v>93.75</v>
+        <v>223</v>
       </c>
       <c r="E4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>24705</v>
+      </c>
+      <c r="B5" t="s">
         <v>9</v>
+      </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
+      <c r="D5">
+        <v>160</v>
+      </c>
+      <c r="E5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>25899</v>
+      </c>
+      <c r="B6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6">
+        <v>340</v>
+      </c>
+      <c r="E6" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/uploads/module_4_701.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_701.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="17">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,16 +37,31 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>لوبيا الضحى بلدى - 500 جم</t>
-  </si>
-  <si>
-    <t>ميزة أرز رفيع- 1 كجم</t>
-  </si>
-  <si>
-    <t>ماكسي كـولا - 2 لتر</t>
-  </si>
-  <si>
-    <t>بيبسى كانز ستار زيادة %10- 355 مل</t>
+    <t>فاين مناديل فلافي جيب- 10 باكت</t>
+  </si>
+  <si>
+    <t>عصير جهينة مانجو - 1 لتر</t>
+  </si>
+  <si>
+    <t>امريكانا بيفي بلوبيف - 340 جم</t>
+  </si>
+  <si>
+    <t>زيت حلوة خليط - 2.25 لتر</t>
+  </si>
+  <si>
+    <t>شويبس رمان - 300 مل</t>
+  </si>
+  <si>
+    <t>شويبس جولد خوخ - 300 مل</t>
+  </si>
+  <si>
+    <t>بن ابو عوف فاتح محوج صفيح - 200 جم</t>
+  </si>
+  <si>
+    <t>شويبس رمان بلاستيك - 250 مل</t>
+  </si>
+  <si>
+    <t>فاين مناديل تواليت كمفورت 24 رول20+ 4مجانا 24 رول</t>
   </si>
   <si>
     <t>YES</t>
@@ -407,7 +422,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -435,87 +450,189 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>1063</v>
+        <v>308</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>1835</v>
+        <v>185</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>1063</v>
+        <v>412</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>91.75</v>
+        <v>358.75</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>11555</v>
+        <v>424</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D4">
-        <v>223</v>
+        <v>1320</v>
       </c>
       <c r="E4" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>24705</v>
+        <v>424</v>
       </c>
       <c r="B5" t="s">
         <v>9</v>
       </c>
       <c r="C5">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D5">
-        <v>160</v>
+        <v>55</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>25899</v>
+        <v>1091</v>
       </c>
       <c r="B6" t="s">
         <v>10</v>
       </c>
       <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>625</v>
+      </c>
+      <c r="E6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>1654</v>
+      </c>
+      <c r="B7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7">
         <v>2</v>
       </c>
-      <c r="D6">
-        <v>340</v>
-      </c>
-      <c r="E6" t="s">
-        <v>11</v>
+      <c r="D7">
+        <v>325</v>
+      </c>
+      <c r="E7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>1655</v>
+      </c>
+      <c r="B8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8">
+        <v>2</v>
+      </c>
+      <c r="D8">
+        <v>327.5</v>
+      </c>
+      <c r="E8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>3905</v>
+      </c>
+      <c r="B9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9">
+        <v>14</v>
+      </c>
+      <c r="D9">
+        <v>194</v>
+      </c>
+      <c r="E9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>3905</v>
+      </c>
+      <c r="B10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10">
+        <v>2328</v>
+      </c>
+      <c r="E10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>11685</v>
+      </c>
+      <c r="B11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11">
+        <v>2</v>
+      </c>
+      <c r="D11">
+        <v>112</v>
+      </c>
+      <c r="E11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>13269</v>
+      </c>
+      <c r="B12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12">
+        <v>29</v>
+      </c>
+      <c r="D12">
+        <v>388</v>
+      </c>
+      <c r="E12" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/uploads/module_4_701.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_701.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="10">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,31 +37,10 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>فاين مناديل فلافي جيب- 10 باكت</t>
-  </si>
-  <si>
-    <t>عصير جهينة مانجو - 1 لتر</t>
-  </si>
-  <si>
-    <t>امريكانا بيفي بلوبيف - 340 جم</t>
-  </si>
-  <si>
-    <t>زيت حلوة خليط - 2.25 لتر</t>
-  </si>
-  <si>
-    <t>شويبس رمان - 300 مل</t>
-  </si>
-  <si>
-    <t>شويبس جولد خوخ - 300 مل</t>
-  </si>
-  <si>
-    <t>بن ابو عوف فاتح محوج صفيح - 200 جم</t>
-  </si>
-  <si>
-    <t>شويبس رمان بلاستيك - 250 مل</t>
-  </si>
-  <si>
-    <t>فاين مناديل تواليت كمفورت 24 رول20+ 4مجانا 24 رول</t>
+    <t>كيك سويس روول بكريمه الفراوله - 6 قطعه</t>
+  </si>
+  <si>
+    <t>أمريكانا فول سادة 20% خصم-( 12عرض*2عبوة ) 400 جم</t>
   </si>
   <si>
     <t>YES</t>
@@ -422,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -450,7 +429,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>308</v>
+        <v>11309</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
@@ -459,180 +438,61 @@
         <v>1</v>
       </c>
       <c r="D2">
-        <v>185</v>
+        <v>564</v>
       </c>
       <c r="E2" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>412</v>
+        <v>11309</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D3">
-        <v>358.75</v>
+        <v>47</v>
       </c>
       <c r="E3" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>424</v>
+        <v>13118</v>
       </c>
       <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
+      <c r="D4">
+        <v>411</v>
+      </c>
+      <c r="E4" t="s">
         <v>9</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>1320</v>
-      </c>
-      <c r="E4" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>424</v>
+        <v>13118</v>
       </c>
       <c r="B5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5">
+        <v>431</v>
+      </c>
+      <c r="D5">
+        <v>34.25</v>
+      </c>
+      <c r="E5" t="s">
         <v>9</v>
-      </c>
-      <c r="C5">
-        <v>11</v>
-      </c>
-      <c r="D5">
-        <v>55</v>
-      </c>
-      <c r="E5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>1091</v>
-      </c>
-      <c r="B6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6">
-        <v>625</v>
-      </c>
-      <c r="E6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>1654</v>
-      </c>
-      <c r="B7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7">
-        <v>2</v>
-      </c>
-      <c r="D7">
-        <v>325</v>
-      </c>
-      <c r="E7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>1655</v>
-      </c>
-      <c r="B8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8">
-        <v>2</v>
-      </c>
-      <c r="D8">
-        <v>327.5</v>
-      </c>
-      <c r="E8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>3905</v>
-      </c>
-      <c r="B9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9">
-        <v>14</v>
-      </c>
-      <c r="D9">
-        <v>194</v>
-      </c>
-      <c r="E9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>3905</v>
-      </c>
-      <c r="B10" t="s">
-        <v>13</v>
-      </c>
-      <c r="C10">
-        <v>1</v>
-      </c>
-      <c r="D10">
-        <v>2328</v>
-      </c>
-      <c r="E10" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>11685</v>
-      </c>
-      <c r="B11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C11">
-        <v>2</v>
-      </c>
-      <c r="D11">
-        <v>112</v>
-      </c>
-      <c r="E11" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>13269</v>
-      </c>
-      <c r="B12" t="s">
-        <v>15</v>
-      </c>
-      <c r="C12">
-        <v>29</v>
-      </c>
-      <c r="D12">
-        <v>388</v>
-      </c>
-      <c r="E12" t="s">
-        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/uploads/module_4_701.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_701.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="12">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,10 +37,16 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>كيك سويس روول بكريمه الفراوله - 6 قطعه</t>
-  </si>
-  <si>
-    <t>أمريكانا فول سادة 20% خصم-( 12عرض*2عبوة ) 400 جم</t>
+    <t>امريكانا بيفي بلوبيف - 340 جم</t>
+  </si>
+  <si>
+    <t>شاى ليبتون خرز - 250 جم</t>
+  </si>
+  <si>
+    <t>فانتا برتقال جيب - 240 مل</t>
+  </si>
+  <si>
+    <t>كوكا كولا زيرو - 15 جنيه 0.95 لتر</t>
   </si>
   <si>
     <t>YES</t>
@@ -401,7 +407,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -429,70 +435,104 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>11309</v>
+        <v>424</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D2">
-        <v>564</v>
+        <v>56</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>11309</v>
+        <v>424</v>
       </c>
       <c r="B3" t="s">
         <v>7</v>
       </c>
       <c r="C3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>47</v>
+        <v>1344</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>13118</v>
+        <v>491</v>
       </c>
       <c r="B4" t="s">
         <v>8</v>
       </c>
       <c r="C4">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D4">
-        <v>411</v>
+        <v>70</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>13118</v>
+        <v>491</v>
       </c>
       <c r="B5" t="s">
         <v>8</v>
       </c>
       <c r="C5">
-        <v>431</v>
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>34.25</v>
+        <v>3360</v>
       </c>
       <c r="E5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>624</v>
+      </c>
+      <c r="B6" t="s">
         <v>9</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6">
+        <v>291.5</v>
+      </c>
+      <c r="E6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>2803</v>
+      </c>
+      <c r="B7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
+      <c r="D7">
+        <v>140</v>
+      </c>
+      <c r="E7" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/uploads/module_4_701.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_701.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="11">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,13 +37,13 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>كابتشينو كوفى بريك كلاسيك 8 ظرف - 18.5 جم</t>
-  </si>
-  <si>
-    <t>شاى الكبوس ناعم عرض 65 ج - 200 جم</t>
-  </si>
-  <si>
-    <t>قهوة ابو عوف 3*1 سريعة التحضير - 18 جم</t>
+    <t>كوكا كولا زيرو - 320 مل</t>
+  </si>
+  <si>
+    <t>ستينج فراولة تربو بلاستيك - 400 مل</t>
+  </si>
+  <si>
+    <t>فاين سوبر مناديل مطبخ 5+1 رول * 2 طبقة 6 رول</t>
   </si>
   <si>
     <t>YES</t>
@@ -404,7 +404,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -432,16 +432,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>2057</v>
+        <v>4246</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2">
-        <v>1542</v>
+        <v>322.5</v>
       </c>
       <c r="E2" t="s">
         <v>10</v>
@@ -449,16 +449,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>2057</v>
+        <v>11234</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D3">
-        <v>64.25</v>
+        <v>164</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -466,69 +466,18 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>9081</v>
+        <v>13274</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C4">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="D4">
-        <v>60.75</v>
+        <v>234.75</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>9081</v>
-      </c>
-      <c r="B5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>1458</v>
-      </c>
-      <c r="E5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>10537</v>
-      </c>
-      <c r="B6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6">
-        <v>768</v>
-      </c>
-      <c r="E6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>10537</v>
-      </c>
-      <c r="B7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7">
-        <v>3</v>
-      </c>
-      <c r="D7">
-        <v>64</v>
-      </c>
-      <c r="E7" t="s">
         <v>10</v>
       </c>
     </row>

--- a/Pricing Logic/modules/uploads/module_4_701.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_701.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,13 +37,7 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>كوكا كولا زيرو - 320 مل</t>
-  </si>
-  <si>
-    <t>ستينج فراولة تربو بلاستيك - 400 مل</t>
-  </si>
-  <si>
-    <t>فاين سوبر مناديل مطبخ 5+1 رول * 2 طبقة 6 رول</t>
+    <t>مكرونة الملكة فرن - 400 جم</t>
   </si>
   <si>
     <t>YES</t>
@@ -404,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -432,53 +426,19 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>4246</v>
+        <v>25</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>322.5</v>
+        <v>256.75</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>11234</v>
-      </c>
-      <c r="B3" t="s">
         <v>8</v>
-      </c>
-      <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>164</v>
-      </c>
-      <c r="E3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>13274</v>
-      </c>
-      <c r="B4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4">
-        <v>29</v>
-      </c>
-      <c r="D4">
-        <v>234.75</v>
-      </c>
-      <c r="E4" t="s">
-        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/uploads/module_4_701.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_701.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="9">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,7 +37,7 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>مكرونة الملكة فرن - 400 جم</t>
+    <t>حلو الشام رايت شيف جديد - 18 جم</t>
   </si>
   <si>
     <t>YES</t>
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -426,7 +426,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>25</v>
+        <v>13326</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
@@ -435,9 +435,26 @@
         <v>1</v>
       </c>
       <c r="D2">
-        <v>256.75</v>
+        <v>498</v>
       </c>
       <c r="E2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>13326</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3">
+        <v>3</v>
+      </c>
+      <c r="D3">
+        <v>41.5</v>
+      </c>
+      <c r="E3" t="s">
         <v>8</v>
       </c>
     </row>

--- a/Pricing Logic/modules/uploads/module_4_701.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_701.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="31">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,7 +37,73 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>حلو الشام رايت شيف جديد - 18 جم</t>
+    <t>شهرزاد بامية زيرو - 400 جم</t>
+  </si>
+  <si>
+    <t>شهرزاد بامية ممتازة - 400 جم</t>
+  </si>
+  <si>
+    <t>باندا مثلثات - 8 قطعه</t>
+  </si>
+  <si>
+    <t>باندا مثلثات - 16 قطعه</t>
+  </si>
+  <si>
+    <t>باندا جورمية مثلثات - 8 قطعه</t>
+  </si>
+  <si>
+    <t>باندا جورمية مثلثات - 16 قطعه</t>
+  </si>
+  <si>
+    <t>باندا جورمية جبنة كريمى  بالقشطة - 4 قطعه</t>
+  </si>
+  <si>
+    <t>باندا جورمية جبنة مربعات ب القشطة - 6 قطعه</t>
+  </si>
+  <si>
+    <t>باندا جورمية مربعات جبنة بالقشطة - 8 قطعه</t>
+  </si>
+  <si>
+    <t>جبنة باندا فيتا  - 500 جم</t>
+  </si>
+  <si>
+    <t>جبنة باندا رومى - 250 جم</t>
+  </si>
+  <si>
+    <t>جبنة باندا شيدر - 500 جم</t>
+  </si>
+  <si>
+    <t>جبنة باندا رومى - 500 جم</t>
+  </si>
+  <si>
+    <t>جبنة باندا شيدر - 250 جم</t>
+  </si>
+  <si>
+    <t>جبنة باندا بسطرمة  - 125 جم</t>
+  </si>
+  <si>
+    <t>جبنة باندا بسطرمة - 250 جم</t>
+  </si>
+  <si>
+    <t>جبنة باندا بسطرمة - 500 جم</t>
+  </si>
+  <si>
+    <t>جبنة ديرى فيتا بلس  - 125 جم</t>
+  </si>
+  <si>
+    <t>جبنة ديرى فيتا  - 250 جم</t>
+  </si>
+  <si>
+    <t>جبنة ديرى فيتا بلس - 500 جم</t>
+  </si>
+  <si>
+    <t>جبنة باندا فيتا 250 جرام</t>
+  </si>
+  <si>
+    <t>جبنة باندا فيتا 125 جرام</t>
+  </si>
+  <si>
+    <t>عرض باندا ( 2علبة باندا250 جم + علبة فول باندا 400جم) - 900 جم</t>
   </si>
   <si>
     <t>YES</t>
@@ -398,7 +464,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -426,36 +492,614 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>13326</v>
+        <v>7523</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="D2">
-        <v>498</v>
+        <v>170</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>13326</v>
+        <v>7523</v>
       </c>
       <c r="B3" t="s">
         <v>7</v>
       </c>
       <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>680</v>
+      </c>
+      <c r="E3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>7523</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4">
+        <v>16</v>
+      </c>
+      <c r="D4">
+        <v>340</v>
+      </c>
+      <c r="E4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>7523</v>
+      </c>
+      <c r="B5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5">
+        <v>7</v>
+      </c>
+      <c r="D5">
+        <v>34</v>
+      </c>
+      <c r="E5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>8139</v>
+      </c>
+      <c r="B6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6">
+        <v>16</v>
+      </c>
+      <c r="D6">
+        <v>210</v>
+      </c>
+      <c r="E6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>8139</v>
+      </c>
+      <c r="B7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>420</v>
+      </c>
+      <c r="E7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>8139</v>
+      </c>
+      <c r="B8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8">
+        <v>7</v>
+      </c>
+      <c r="D8">
+        <v>21</v>
+      </c>
+      <c r="E8" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>8139</v>
+      </c>
+      <c r="B9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9">
+        <v>15</v>
+      </c>
+      <c r="D9">
+        <v>105</v>
+      </c>
+      <c r="E9" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>21704</v>
+      </c>
+      <c r="B10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10">
+        <v>1386</v>
+      </c>
+      <c r="E10" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>21704</v>
+      </c>
+      <c r="B11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11">
         <v>3</v>
       </c>
-      <c r="D3">
-        <v>41.5</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
+      <c r="D11">
+        <v>38.5</v>
+      </c>
+      <c r="E11" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>21705</v>
+      </c>
+      <c r="B12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12">
+        <v>1740</v>
+      </c>
+      <c r="E12" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>21705</v>
+      </c>
+      <c r="B13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13">
+        <v>3</v>
+      </c>
+      <c r="D13">
+        <v>72.5</v>
+      </c>
+      <c r="E13" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>21706</v>
+      </c>
+      <c r="B14" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14">
+        <v>3</v>
+      </c>
+      <c r="D14">
+        <v>26.75</v>
+      </c>
+      <c r="E14" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>21706</v>
+      </c>
+      <c r="B15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15">
+        <v>963</v>
+      </c>
+      <c r="E15" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>21707</v>
+      </c>
+      <c r="B16" t="s">
+        <v>12</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16">
+        <v>1272</v>
+      </c>
+      <c r="E16" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17">
+        <v>21707</v>
+      </c>
+      <c r="B17" t="s">
+        <v>12</v>
+      </c>
+      <c r="C17">
+        <v>3</v>
+      </c>
+      <c r="D17">
+        <v>53</v>
+      </c>
+      <c r="E17" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18">
+        <v>21708</v>
+      </c>
+      <c r="B18" t="s">
+        <v>13</v>
+      </c>
+      <c r="C18">
+        <v>3</v>
+      </c>
+      <c r="D18">
+        <v>26</v>
+      </c>
+      <c r="E18" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19">
+        <v>21708</v>
+      </c>
+      <c r="B19" t="s">
+        <v>13</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+      <c r="D19">
+        <v>1040</v>
+      </c>
+      <c r="E19" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20">
+        <v>21709</v>
+      </c>
+      <c r="B20" t="s">
+        <v>14</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20">
+        <v>1132.5</v>
+      </c>
+      <c r="E20" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21">
+        <v>21709</v>
+      </c>
+      <c r="B21" t="s">
+        <v>14</v>
+      </c>
+      <c r="C21">
+        <v>3</v>
+      </c>
+      <c r="D21">
+        <v>37.75</v>
+      </c>
+      <c r="E21" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22">
+        <v>21710</v>
+      </c>
+      <c r="B22" t="s">
+        <v>15</v>
+      </c>
+      <c r="C22">
+        <v>3</v>
+      </c>
+      <c r="D22">
+        <v>49</v>
+      </c>
+      <c r="E22" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23">
+        <v>21710</v>
+      </c>
+      <c r="B23" t="s">
+        <v>15</v>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
+      <c r="D23">
+        <v>1470</v>
+      </c>
+      <c r="E23" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24">
+        <v>21745</v>
+      </c>
+      <c r="B24" t="s">
+        <v>16</v>
+      </c>
+      <c r="C24">
+        <v>2</v>
+      </c>
+      <c r="D24">
+        <v>417.5</v>
+      </c>
+      <c r="E24" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25">
+        <v>21752</v>
+      </c>
+      <c r="B25" t="s">
+        <v>17</v>
+      </c>
+      <c r="C25">
+        <v>2</v>
+      </c>
+      <c r="D25">
+        <v>474.25</v>
+      </c>
+      <c r="E25" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26">
+        <v>21754</v>
+      </c>
+      <c r="B26" t="s">
+        <v>18</v>
+      </c>
+      <c r="C26">
+        <v>2</v>
+      </c>
+      <c r="D26">
+        <v>417.5</v>
+      </c>
+      <c r="E26" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27">
+        <v>21771</v>
+      </c>
+      <c r="B27" t="s">
+        <v>19</v>
+      </c>
+      <c r="C27">
+        <v>2</v>
+      </c>
+      <c r="D27">
+        <v>417.5</v>
+      </c>
+      <c r="E27" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28">
+        <v>21774</v>
+      </c>
+      <c r="B28" t="s">
+        <v>20</v>
+      </c>
+      <c r="C28">
+        <v>2</v>
+      </c>
+      <c r="D28">
+        <v>474.25</v>
+      </c>
+      <c r="E28" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29">
+        <v>21777</v>
+      </c>
+      <c r="B29" t="s">
+        <v>21</v>
+      </c>
+      <c r="C29">
+        <v>2</v>
+      </c>
+      <c r="D29">
+        <v>368.5</v>
+      </c>
+      <c r="E29" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30">
+        <v>21778</v>
+      </c>
+      <c r="B30" t="s">
+        <v>22</v>
+      </c>
+      <c r="C30">
+        <v>2</v>
+      </c>
+      <c r="D30">
+        <v>474.25</v>
+      </c>
+      <c r="E30" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31">
+        <v>21779</v>
+      </c>
+      <c r="B31" t="s">
+        <v>23</v>
+      </c>
+      <c r="C31">
+        <v>2</v>
+      </c>
+      <c r="D31">
+        <v>417.5</v>
+      </c>
+      <c r="E31" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32">
+        <v>21781</v>
+      </c>
+      <c r="B32" t="s">
+        <v>24</v>
+      </c>
+      <c r="C32">
+        <v>2</v>
+      </c>
+      <c r="D32">
+        <v>283</v>
+      </c>
+      <c r="E32" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33">
+        <v>21783</v>
+      </c>
+      <c r="B33" t="s">
+        <v>25</v>
+      </c>
+      <c r="C33">
+        <v>2</v>
+      </c>
+      <c r="D33">
+        <v>356.5</v>
+      </c>
+      <c r="E33" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34">
+        <v>21789</v>
+      </c>
+      <c r="B34" t="s">
+        <v>26</v>
+      </c>
+      <c r="C34">
+        <v>2</v>
+      </c>
+      <c r="D34">
+        <v>310</v>
+      </c>
+      <c r="E34" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35">
+        <v>22125</v>
+      </c>
+      <c r="B35" t="s">
+        <v>27</v>
+      </c>
+      <c r="C35">
+        <v>2</v>
+      </c>
+      <c r="D35">
+        <v>474.25</v>
+      </c>
+      <c r="E35" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36">
+        <v>22126</v>
+      </c>
+      <c r="B36" t="s">
+        <v>28</v>
+      </c>
+      <c r="C36">
+        <v>2</v>
+      </c>
+      <c r="D36">
+        <v>368.5</v>
+      </c>
+      <c r="E36" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37">
+        <v>25775</v>
+      </c>
+      <c r="B37" t="s">
+        <v>29</v>
+      </c>
+      <c r="C37">
+        <v>2</v>
+      </c>
+      <c r="D37">
+        <v>280</v>
+      </c>
+      <c r="E37" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/uploads/module_4_701.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_701.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="29">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,10 +37,67 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>صابون كامى رومانسية - 110 جم</t>
-  </si>
-  <si>
-    <t>نوفي فينجرز شيكولاتة بيضاء - 5 جنية</t>
+    <t>زيت كريستال الممتاز خليط - 1 لتر</t>
+  </si>
+  <si>
+    <t>زيت كريستال الممتاز خليط - 700 مل</t>
+  </si>
+  <si>
+    <t>زيت قلية خليط - 1 لتر</t>
+  </si>
+  <si>
+    <t>زيت حبوبة خليط - 900 مل</t>
+  </si>
+  <si>
+    <t>هلا زيت عباد الشمس- 500 مل</t>
+  </si>
+  <si>
+    <t>زيت حلوة خليط - 2.25 لتر</t>
+  </si>
+  <si>
+    <t>زيت حبوبة خليط - 700 مل</t>
+  </si>
+  <si>
+    <t>زيت حبوبة خليط - 1 لتر</t>
+  </si>
+  <si>
+    <t>زيت صنى خليط عباد الشمس - 2.4 لتر</t>
+  </si>
+  <si>
+    <t>زيت كريستال عباد الشمس 6 زجاجة - 700 مل</t>
+  </si>
+  <si>
+    <t>زيت كريستال عباد الشمس 4 زجاجة - 2.2 لتر</t>
+  </si>
+  <si>
+    <t>زيت كريستال ذرة 4 زجاجة - 2.2 لتر</t>
+  </si>
+  <si>
+    <t>زيت كريستال ذرة 6 زجاجة - 1.6 لتر</t>
+  </si>
+  <si>
+    <t>زيت كريستال عباد الشمس 6 زجاجة - 1.6 لتر</t>
+  </si>
+  <si>
+    <t>زيت حلوة خليط - 4.5 لتر</t>
+  </si>
+  <si>
+    <t>صنى خليط زيت عباد الشمس  - 1.75 لتر</t>
+  </si>
+  <si>
+    <t>سندة زيت خليط - 1 لتر</t>
+  </si>
+  <si>
+    <t>زيت كريستال ذرة - 3.5 لتر</t>
+  </si>
+  <si>
+    <t>زيت كريستال ذرة 6 زجاجة - 1 لتر</t>
+  </si>
+  <si>
+    <t>زيت كريستال الممتاز خليط - 2.5 لتر</t>
+  </si>
+  <si>
+    <t>زيت ثمرات خليط - 1 لتر</t>
   </si>
   <si>
     <t>YES</t>
@@ -401,7 +458,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -429,7 +486,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>8286</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
@@ -438,61 +495,350 @@
         <v>1</v>
       </c>
       <c r="D2">
-        <v>696</v>
+        <v>866</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>8286</v>
+        <v>448</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>58</v>
+        <v>625</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21687</v>
+        <v>470</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
       <c r="D4">
-        <v>288</v>
+        <v>863.5</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21687</v>
+        <v>823</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D5">
+        <v>764.5</v>
+      </c>
+      <c r="E5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>925</v>
+      </c>
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>550.75</v>
+      </c>
+      <c r="E6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>1091</v>
+      </c>
+      <c r="B7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>655</v>
+      </c>
+      <c r="E7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>1490</v>
+      </c>
+      <c r="B8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>604</v>
+      </c>
+      <c r="E8" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>1492</v>
+      </c>
+      <c r="B9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <v>860</v>
+      </c>
+      <c r="E9" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>2608</v>
+      </c>
+      <c r="B10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10">
+        <v>725.25</v>
+      </c>
+      <c r="E10" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>2878</v>
+      </c>
+      <c r="B11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <v>388.25</v>
+      </c>
+      <c r="E11" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>2879</v>
+      </c>
+      <c r="B12" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12">
+        <v>810</v>
+      </c>
+      <c r="E12" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>2916</v>
+      </c>
+      <c r="B13" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13">
+        <v>955</v>
+      </c>
+      <c r="E13" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>2934</v>
+      </c>
+      <c r="B14" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14">
+        <v>1066</v>
+      </c>
+      <c r="E14" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>2935</v>
+      </c>
+      <c r="B15" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15">
+        <v>892.5</v>
+      </c>
+      <c r="E15" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>4203</v>
+      </c>
+      <c r="B16" t="s">
+        <v>21</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16">
+        <v>640</v>
+      </c>
+      <c r="E16" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17">
+        <v>6421</v>
+      </c>
+      <c r="B17" t="s">
+        <v>22</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17">
+        <v>516.75</v>
+      </c>
+      <c r="E17" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18">
+        <v>6497</v>
+      </c>
+      <c r="B18" t="s">
+        <v>23</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18">
+        <v>855</v>
+      </c>
+      <c r="E18" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19">
+        <v>7520</v>
+      </c>
+      <c r="B19" t="s">
         <v>24</v>
       </c>
-      <c r="E5" t="s">
-        <v>9</v>
+      <c r="C19">
+        <v>1</v>
+      </c>
+      <c r="D19">
+        <v>1464.75</v>
+      </c>
+      <c r="E19" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20">
+        <v>11962</v>
+      </c>
+      <c r="B20" t="s">
+        <v>25</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20">
+        <v>681.75</v>
+      </c>
+      <c r="E20" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21">
+        <v>11965</v>
+      </c>
+      <c r="B21" t="s">
+        <v>26</v>
+      </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
+      <c r="D21">
+        <v>705.25</v>
+      </c>
+      <c r="E21" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22">
+        <v>12923</v>
+      </c>
+      <c r="B22" t="s">
+        <v>27</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
+      </c>
+      <c r="D22">
+        <v>855</v>
+      </c>
+      <c r="E22" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/uploads/module_4_701.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_701.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="20">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,67 +37,40 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>زيت كريستال الممتاز خليط - 1 لتر</t>
-  </si>
-  <si>
-    <t>زيت كريستال الممتاز خليط - 700 مل</t>
-  </si>
-  <si>
-    <t>زيت قلية خليط - 1 لتر</t>
+    <t>زيت قلية خليط - 2.1 لتر</t>
   </si>
   <si>
     <t>زيت حبوبة خليط - 900 مل</t>
   </si>
   <si>
-    <t>هلا زيت عباد الشمس- 500 مل</t>
-  </si>
-  <si>
-    <t>زيت حلوة خليط - 2.25 لتر</t>
-  </si>
-  <si>
-    <t>زيت حبوبة خليط - 700 مل</t>
-  </si>
-  <si>
-    <t>زيت حبوبة خليط - 1 لتر</t>
-  </si>
-  <si>
-    <t>زيت صنى خليط عباد الشمس - 2.4 لتر</t>
-  </si>
-  <si>
-    <t>زيت كريستال عباد الشمس 6 زجاجة - 700 مل</t>
-  </si>
-  <si>
-    <t>زيت كريستال عباد الشمس 4 زجاجة - 2.2 لتر</t>
-  </si>
-  <si>
-    <t>زيت كريستال ذرة 4 زجاجة - 2.2 لتر</t>
-  </si>
-  <si>
-    <t>زيت كريستال ذرة 6 زجاجة - 1.6 لتر</t>
-  </si>
-  <si>
-    <t>زيت كريستال عباد الشمس 6 زجاجة - 1.6 لتر</t>
-  </si>
-  <si>
-    <t>زيت حلوة خليط - 4.5 لتر</t>
-  </si>
-  <si>
-    <t>صنى خليط زيت عباد الشمس  - 1.75 لتر</t>
-  </si>
-  <si>
-    <t>سندة زيت خليط - 1 لتر</t>
-  </si>
-  <si>
-    <t>زيت كريستال ذرة - 3.5 لتر</t>
-  </si>
-  <si>
-    <t>زيت كريستال ذرة 6 زجاجة - 1 لتر</t>
-  </si>
-  <si>
-    <t>زيت كريستال الممتاز خليط - 2.5 لتر</t>
-  </si>
-  <si>
-    <t>زيت ثمرات خليط - 1 لتر</t>
+    <t>جبنة دومتى فيتا بلس - 125 جم</t>
+  </si>
+  <si>
+    <t>جبنة دومتى فيتا بلس رومى - 125 جم</t>
+  </si>
+  <si>
+    <t>جبنة دومتى فيتا بلس زيتون - 125 جم</t>
+  </si>
+  <si>
+    <t>دومتي جبنة فيتا بلس - 250 جم</t>
+  </si>
+  <si>
+    <t>دومتي جبنة فيتا بلس بالزيتون  - 250 مل</t>
+  </si>
+  <si>
+    <t>جبنة دومتي بلس بالزيتون - 500 جم</t>
+  </si>
+  <si>
+    <t>دومتي جبنة اسطنبولي بلس - 500 جم</t>
+  </si>
+  <si>
+    <t>دومتي جبنة فلمنك - 500 جم</t>
+  </si>
+  <si>
+    <t>دومتي جبنة فيتا بلس بسطرمة - 500 جم</t>
+  </si>
+  <si>
+    <t>جبنه دومتى جولد -- 250 جم</t>
   </si>
   <si>
     <t>YES</t>
@@ -458,7 +431,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -486,7 +459,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>9</v>
+        <v>471</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
@@ -495,15 +468,15 @@
         <v>1</v>
       </c>
       <c r="D2">
-        <v>866</v>
+        <v>612.25</v>
       </c>
       <c r="E2" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>448</v>
+        <v>823</v>
       </c>
       <c r="B3" t="s">
         <v>8</v>
@@ -512,15 +485,15 @@
         <v>1</v>
       </c>
       <c r="D3">
-        <v>625</v>
+        <v>777</v>
       </c>
       <c r="E3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>470</v>
+        <v>903</v>
       </c>
       <c r="B4" t="s">
         <v>9</v>
@@ -529,15 +502,15 @@
         <v>1</v>
       </c>
       <c r="D4">
-        <v>863.5</v>
+        <v>402</v>
       </c>
       <c r="E4" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>823</v>
+        <v>11293</v>
       </c>
       <c r="B5" t="s">
         <v>10</v>
@@ -546,15 +519,15 @@
         <v>1</v>
       </c>
       <c r="D5">
-        <v>764.5</v>
+        <v>402</v>
       </c>
       <c r="E5" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>925</v>
+        <v>13210</v>
       </c>
       <c r="B6" t="s">
         <v>11</v>
@@ -563,282 +536,129 @@
         <v>1</v>
       </c>
       <c r="D6">
-        <v>550.75</v>
+        <v>402</v>
       </c>
       <c r="E6" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>1091</v>
+        <v>19980</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7">
-        <v>655</v>
+        <v>519</v>
       </c>
       <c r="E7" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>1490</v>
+        <v>19982</v>
       </c>
       <c r="B8" t="s">
         <v>13</v>
       </c>
       <c r="C8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D8">
-        <v>604</v>
+        <v>519</v>
       </c>
       <c r="E8" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>1492</v>
+        <v>19983</v>
       </c>
       <c r="B9" t="s">
         <v>14</v>
       </c>
       <c r="C9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D9">
-        <v>860</v>
+        <v>460</v>
       </c>
       <c r="E9" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>2608</v>
+        <v>19985</v>
       </c>
       <c r="B10" t="s">
         <v>15</v>
       </c>
       <c r="C10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D10">
-        <v>725.25</v>
+        <v>460</v>
       </c>
       <c r="E10" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>2878</v>
+        <v>19987</v>
       </c>
       <c r="B11" t="s">
         <v>16</v>
       </c>
       <c r="C11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D11">
-        <v>388.25</v>
+        <v>460</v>
       </c>
       <c r="E11" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>2879</v>
+        <v>19989</v>
       </c>
       <c r="B12" t="s">
         <v>17</v>
       </c>
       <c r="C12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D12">
-        <v>810</v>
+        <v>460</v>
       </c>
       <c r="E12" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>2916</v>
+        <v>26103</v>
       </c>
       <c r="B13" t="s">
         <v>18</v>
       </c>
       <c r="C13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D13">
-        <v>955</v>
+        <v>654</v>
       </c>
       <c r="E13" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>2934</v>
-      </c>
-      <c r="B14" t="s">
-        <v>19</v>
-      </c>
-      <c r="C14">
-        <v>1</v>
-      </c>
-      <c r="D14">
-        <v>1066</v>
-      </c>
-      <c r="E14" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>2935</v>
-      </c>
-      <c r="B15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C15">
-        <v>1</v>
-      </c>
-      <c r="D15">
-        <v>892.5</v>
-      </c>
-      <c r="E15" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>4203</v>
-      </c>
-      <c r="B16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C16">
-        <v>1</v>
-      </c>
-      <c r="D16">
-        <v>640</v>
-      </c>
-      <c r="E16" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17">
-        <v>6421</v>
-      </c>
-      <c r="B17" t="s">
-        <v>22</v>
-      </c>
-      <c r="C17">
-        <v>1</v>
-      </c>
-      <c r="D17">
-        <v>516.75</v>
-      </c>
-      <c r="E17" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18">
-        <v>6497</v>
-      </c>
-      <c r="B18" t="s">
-        <v>23</v>
-      </c>
-      <c r="C18">
-        <v>1</v>
-      </c>
-      <c r="D18">
-        <v>855</v>
-      </c>
-      <c r="E18" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19">
-        <v>7520</v>
-      </c>
-      <c r="B19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C19">
-        <v>1</v>
-      </c>
-      <c r="D19">
-        <v>1464.75</v>
-      </c>
-      <c r="E19" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20">
-        <v>11962</v>
-      </c>
-      <c r="B20" t="s">
-        <v>25</v>
-      </c>
-      <c r="C20">
-        <v>1</v>
-      </c>
-      <c r="D20">
-        <v>681.75</v>
-      </c>
-      <c r="E20" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21">
-        <v>11965</v>
-      </c>
-      <c r="B21" t="s">
-        <v>26</v>
-      </c>
-      <c r="C21">
-        <v>1</v>
-      </c>
-      <c r="D21">
-        <v>705.25</v>
-      </c>
-      <c r="E21" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22">
-        <v>12923</v>
-      </c>
-      <c r="B22" t="s">
-        <v>27</v>
-      </c>
-      <c r="C22">
-        <v>1</v>
-      </c>
-      <c r="D22">
-        <v>855</v>
-      </c>
-      <c r="E22" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/uploads/module_4_701.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_701.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,40 +37,7 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>زيت قلية خليط - 2.1 لتر</t>
-  </si>
-  <si>
-    <t>زيت حبوبة خليط - 900 مل</t>
-  </si>
-  <si>
-    <t>جبنة دومتى فيتا بلس - 125 جم</t>
-  </si>
-  <si>
-    <t>جبنة دومتى فيتا بلس رومى - 125 جم</t>
-  </si>
-  <si>
-    <t>جبنة دومتى فيتا بلس زيتون - 125 جم</t>
-  </si>
-  <si>
-    <t>دومتي جبنة فيتا بلس - 250 جم</t>
-  </si>
-  <si>
-    <t>دومتي جبنة فيتا بلس بالزيتون  - 250 مل</t>
-  </si>
-  <si>
-    <t>جبنة دومتي بلس بالزيتون - 500 جم</t>
-  </si>
-  <si>
-    <t>دومتي جبنة اسطنبولي بلس - 500 جم</t>
-  </si>
-  <si>
-    <t>دومتي جبنة فلمنك - 500 جم</t>
-  </si>
-  <si>
-    <t>دومتي جبنة فيتا بلس بسطرمة - 500 جم</t>
-  </si>
-  <si>
-    <t>جبنه دومتى جولد -- 250 جم</t>
+    <t>اوكسي سائل أطباق ليمون اصفر- 100 جم</t>
   </si>
   <si>
     <t>YES</t>
@@ -431,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -459,7 +426,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>471</v>
+        <v>11766</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
@@ -468,197 +435,10 @@
         <v>1</v>
       </c>
       <c r="D2">
-        <v>612.25</v>
+        <v>90</v>
       </c>
       <c r="E2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>823</v>
-      </c>
-      <c r="B3" t="s">
         <v>8</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>777</v>
-      </c>
-      <c r="E3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>903</v>
-      </c>
-      <c r="B4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>402</v>
-      </c>
-      <c r="E4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>11293</v>
-      </c>
-      <c r="B5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>402</v>
-      </c>
-      <c r="E5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>13210</v>
-      </c>
-      <c r="B6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6">
-        <v>402</v>
-      </c>
-      <c r="E6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>19980</v>
-      </c>
-      <c r="B7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7">
-        <v>2</v>
-      </c>
-      <c r="D7">
-        <v>519</v>
-      </c>
-      <c r="E7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>19982</v>
-      </c>
-      <c r="B8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8">
-        <v>2</v>
-      </c>
-      <c r="D8">
-        <v>519</v>
-      </c>
-      <c r="E8" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>19983</v>
-      </c>
-      <c r="B9" t="s">
-        <v>14</v>
-      </c>
-      <c r="C9">
-        <v>2</v>
-      </c>
-      <c r="D9">
-        <v>460</v>
-      </c>
-      <c r="E9" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>19985</v>
-      </c>
-      <c r="B10" t="s">
-        <v>15</v>
-      </c>
-      <c r="C10">
-        <v>2</v>
-      </c>
-      <c r="D10">
-        <v>460</v>
-      </c>
-      <c r="E10" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>19987</v>
-      </c>
-      <c r="B11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11">
-        <v>2</v>
-      </c>
-      <c r="D11">
-        <v>460</v>
-      </c>
-      <c r="E11" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>19989</v>
-      </c>
-      <c r="B12" t="s">
-        <v>17</v>
-      </c>
-      <c r="C12">
-        <v>2</v>
-      </c>
-      <c r="D12">
-        <v>460</v>
-      </c>
-      <c r="E12" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>26103</v>
-      </c>
-      <c r="B13" t="s">
-        <v>18</v>
-      </c>
-      <c r="C13">
-        <v>2</v>
-      </c>
-      <c r="D13">
-        <v>654</v>
-      </c>
-      <c r="E13" t="s">
-        <v>19</v>
       </c>
     </row>
   </sheetData>
